--- a/processo_2/synthetic_proposals/PROPOSTA_021/ficha_pontuacao.xlsx
+++ b/processo_2/synthetic_proposals/PROPOSTA_021/ficha_pontuacao.xlsx
@@ -592,13 +592,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr"/>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -703,7 +703,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -726,17 +726,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G14" t="inlineStr"/>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -799,33 +799,17 @@
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Revista Científica Avançada 1</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>51%</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Revista Científica Avançada 2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1460-7443</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
@@ -966,17 +950,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>4</v>
       </c>
       <c r="F26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G26" t="inlineStr"/>
     </row>
@@ -989,7 +973,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1058,7 +1042,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1083,7 +1067,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G31" t="inlineStr"/>
     </row>
@@ -1126,7 +1110,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1149,7 +1133,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1195,7 +1179,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1218,7 +1202,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1241,7 +1225,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1264,7 +1248,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1287,7 +1271,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1310,17 +1294,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
         <v>1.5</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G42" t="inlineStr"/>
     </row>
@@ -1333,17 +1317,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>1.5</v>
       </c>
       <c r="F43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G43" t="inlineStr"/>
     </row>
@@ -1377,13 +1361,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
         <v>2</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G45" t="inlineStr"/>
     </row>
@@ -1551,7 +1535,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1574,7 +1558,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1601,13 +1585,13 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
         <v>50</v>
       </c>
       <c r="F55" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G55" t="inlineStr"/>
     </row>
@@ -1620,7 +1604,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -1643,7 +1627,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1668,7 +1652,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>71.5</v>
+        <v>25</v>
       </c>
       <c r="G58" t="inlineStr"/>
     </row>
@@ -1866,7 +1850,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
-        <v>87.5</v>
+        <v>32</v>
       </c>
       <c r="G68" t="inlineStr"/>
     </row>
